--- a/chion/streams.xlsx
+++ b/chion/streams.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -34,13 +34,64 @@
     <t>note</t>
   </si>
   <si>
+    <t>description</t>
+  </si>
+  <si>
     <t>Twitter પર 希翁／chion〖NKshoujo所属〗6/24初配信</t>
   </si>
   <si>
     <t>https://twitter.com/NKchion/status/1529422590317854720</t>
   </si>
   <si>
+    <t>Twitter</t>
+  </si>
+  <si>
     <t>這裡寫打招呼的用語\n\n我是希翁\n@NKshoujo所屬\n\nLIVE \n#Chionlive\nFANART \n#希翁解剖\n想給我看(監視用)\n#希巴嚕馬\n \nYoutube https://t.co/aElz7uzlrf\n\n最愛的媽媽 / 緜ママ(@wttn3tpkt)\n#新人Vtuver\n\n(1/2)</t>
+  </si>
+  <si>
+    <t>希翁／chion〖NKshoujo所属〗6/24初配信 (@NKchion)</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NKchion/status/1529763980725854208</t>
+  </si>
+  <si>
+    <t>『死既是因一人而來。』\n\n希翁 Chion | Trailer 前導預告片❤️‍\uD83E\uDE79\uD83D\uDC80\n\n◆禮拜日１８：００首播◆\n\n◆Music:  PeriTune 「ChoirWaltz」\nhttps://t.co/czkhck7z6E\n\n◆Movie: Roku66 (@66_Rokuu)\n\n◆Illustration: 畫的人是希翁喔４我喔\nhttps://t.co/T776s67X6j</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NKchion/status/1530127301413056512</t>
+  </si>
+  <si>
+    <t>\uD83D\uDCE2院內放送\uD83D\uDCE2\n\n各位好，初次見面 希翁希翁打呦\n第一次接觸推特，可以拿來收病人嗎？…可以！！\uD83D\uDE0B\n\n雖然很突然但是跟各位施展一下我的讀心醫術。\n\n#即刻入院 #新人Vtuber \n#沒有在打第五劑</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NKchion/status/1530519166138318848</t>
+  </si>
+  <si>
+    <t>\uD83D\uDCE2院內廣播打優\uD83D\uDCE2\n\n明天❕記得來看我52年前做的影片\n\n明日❕52年前のvideo 公開するんだよ！</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NKchion/status/1530880831228882944</t>
+  </si>
+  <si>
+    <t>\uD83D\uDC80『死既是因一人而來。』 | 希翁 Chion | Trailer\n\n希翁 Chion | Trailer 前導預告片❤️‍\uD83E\uDE79\uD83D\uDC80\nhttps://t.co/kINyjPez2Z</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NKchion/status/1530882600621178881</t>
+  </si>
+  <si>
+    <t>25\n#マシュマロを投げ合おう\nhttps://t.co/Hz9XmHN5OJ</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NKchion/status/1530884650474049537</t>
+  </si>
+  <si>
+    <t>\uD83D\uDCE2院內廣播\uD83D\uDCE2\n前導片發出去ㄌ打優\n\n募集感想ㄉ棉花糖/マシュマロください！\n棉花糖/マシュマロ :https://t.co/Vgt8dT1iCW\n\n到時候會一起吃喔!\n我ㄉ棉花糖都是複製文...</t>
+  </si>
+  <si>
+    <t>https://twitter.com/NKchion/status/1531604947653251072</t>
+  </si>
+  <si>
+    <t>幫你們試躺床喔❤️‍\uD83E\uDE79\nベッド温めておきますよ。\n-\n感謝SpiderApple（@spiderapple93）老師繪製的插圖!!貓咪可愛</t>
   </si>
   <si>
     <t>【初配信】💀死靈護士！襲來！❤️‍🩹【希翁／Chion】</t>
@@ -339,6 +390,9 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
@@ -348,13 +402,16 @@
         <v>44706.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -362,47 +419,194 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2">
+        <v>44707.0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="2">
+        <v>44708.0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="2">
+        <v>44709.0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>44710.0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>44710.0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="2">
+        <v>44710.0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="2">
+        <v>44712.0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="2">
         <v>44736.0</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="2"/>
+      <c r="C10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="B12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="D2"/>
     <hyperlink r:id="rId2" ref="D3"/>
+    <hyperlink r:id="rId3" ref="D4"/>
+    <hyperlink r:id="rId4" ref="D5"/>
+    <hyperlink r:id="rId5" ref="D6"/>
+    <hyperlink r:id="rId6" ref="D7"/>
+    <hyperlink r:id="rId7" ref="D8"/>
+    <hyperlink r:id="rId8" ref="D9"/>
+    <hyperlink r:id="rId9" ref="D10"/>
   </hyperlinks>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId10"/>
 </worksheet>
 </file>
--- a/chion/streams.xlsx
+++ b/chion/streams.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -37,75 +37,73 @@
     <t>description</t>
   </si>
   <si>
-    <t>Twitter પર 希翁／chion〖NKshoujo所属〗6/24初配信</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NKchion/status/1529422590317854720</t>
-  </si>
-  <si>
-    <t>Twitter</t>
-  </si>
-  <si>
-    <t>這裡寫打招呼的用語\n\n我是希翁\n@NKshoujo所屬\n\nLIVE \n#Chionlive\nFANART \n#希翁解剖\n想給我看(監視用)\n#希巴嚕馬\n \nYoutube https://t.co/aElz7uzlrf\n\n最愛的媽媽 / 緜ママ(@wttn3tpkt)\n#新人Vtuver\n\n(1/2)</t>
-  </si>
-  <si>
-    <t>希翁／chion〖NKshoujo所属〗6/24初配信 (@NKchion)</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NKchion/status/1529763980725854208</t>
-  </si>
-  <si>
-    <t>『死既是因一人而來。』\n\n希翁 Chion | Trailer 前導預告片❤️‍\uD83E\uDE79\uD83D\uDC80\n\n◆禮拜日１８：００首播◆\n\n◆Music:  PeriTune 「ChoirWaltz」\nhttps://t.co/czkhck7z6E\n\n◆Movie: Roku66 (@66_Rokuu)\n\n◆Illustration: 畫的人是希翁喔４我喔\nhttps://t.co/T776s67X6j</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NKchion/status/1530127301413056512</t>
-  </si>
-  <si>
-    <t>\uD83D\uDCE2院內放送\uD83D\uDCE2\n\n各位好，初次見面 希翁希翁打呦\n第一次接觸推特，可以拿來收病人嗎？…可以！！\uD83D\uDE0B\n\n雖然很突然但是跟各位施展一下我的讀心醫術。\n\n#即刻入院 #新人Vtuber \n#沒有在打第五劑</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NKchion/status/1530519166138318848</t>
-  </si>
-  <si>
-    <t>\uD83D\uDCE2院內廣播打優\uD83D\uDCE2\n\n明天❕記得來看我52年前做的影片\n\n明日❕52年前のvideo 公開するんだよ！</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NKchion/status/1530880831228882944</t>
-  </si>
-  <si>
-    <t>\uD83D\uDC80『死既是因一人而來。』 | 希翁 Chion | Trailer\n\n希翁 Chion | Trailer 前導預告片❤️‍\uD83E\uDE79\uD83D\uDC80\nhttps://t.co/kINyjPez2Z</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NKchion/status/1530882600621178881</t>
-  </si>
-  <si>
-    <t>25\n#マシュマロを投げ合おう\nhttps://t.co/Hz9XmHN5OJ</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NKchion/status/1530884650474049537</t>
-  </si>
-  <si>
-    <t>\uD83D\uDCE2院內廣播\uD83D\uDCE2\n前導片發出去ㄌ打優\n\n募集感想ㄉ棉花糖/マシュマロください！\n棉花糖/マシュマロ :https://t.co/Vgt8dT1iCW\n\n到時候會一起吃喔!\n我ㄉ棉花糖都是複製文...</t>
-  </si>
-  <si>
-    <t>https://twitter.com/NKchion/status/1531604947653251072</t>
-  </si>
-  <si>
-    <t>幫你們試躺床喔❤️‍\uD83E\uDE79\nベッド温めておきますよ。\n-\n感謝SpiderApple（@spiderapple93）老師繪製的插圖!!貓咪可愛</t>
+    <t>你逃離不了的惡夢。</t>
+  </si>
+  <si>
+    <t>https://archive.ragtag.moe/watch?v=dn8YujUr-ZE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=dn8YujUr-ZE</t>
+  </si>
+  <si>
+    <t>自助餐這樣夾要多少錢</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ePY-ZL3U1ng</t>
   </si>
   <si>
     <t>【初配信】💀死靈護士！襲來！❤️‍🩹【希翁／Chion】</t>
   </si>
   <si>
     <t>https://archive.ragtag.moe/watch?v=gHAxaLMeltA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gHAxaLMeltA</t>
+  </si>
+  <si>
+    <t>【病房軼事】讓我看看你們怎麼做事的【希翁／Chion】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=A_7wGcvE3Y4</t>
+  </si>
+  <si>
+    <t>【酷歌回】唱酷歌同時吃棉花糖同時看全身【希翁／Chion】</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=C9yqN3u4kS0</t>
+  </si>
+  <si>
+    <t>歌回</t>
+  </si>
+  <si>
+    <t>【希翁歌回剪輯】Billie Eilish - idontwannabeyouanymore</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lVCV3nChWZo</t>
+  </si>
+  <si>
+    <t>精華</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4GZs7_beNWI</t>
+  </si>
+  <si>
+    <t>【復活】我 復 活 了！【希翁／Chion】</t>
+  </si>
+  <si>
+    <t>https://archive.ragtag.moe/watch?v=IqXr-M0RDvU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IqXr-M0RDvU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d"/>
+    <numFmt numFmtId="165" formatCode="yyyy/m/d"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -138,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -149,6 +147,15 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -399,7 +406,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2">
-        <v>44706.0</v>
+        <v>44716.0</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -407,11 +414,8 @@
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -419,19 +423,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2">
-        <v>44707.0</v>
+        <v>44719.0</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -439,19 +437,16 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2">
-        <v>44708.0</v>
+        <v>44736.0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -459,19 +454,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2">
-        <v>44709.0</v>
+        <v>44737.0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -479,18 +468,15 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2">
-        <v>44710.0</v>
+        <v>44737.0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -499,19 +485,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="2">
-        <v>44710.0</v>
+        <v>44740.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -519,19 +502,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2">
-        <v>44710.0</v>
+        <v>44740.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -539,37 +519,24 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2">
-        <v>44712.0</v>
+        <v>44742.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="2">
-        <v>44736.0</v>
-      </c>
-      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="2"/>
@@ -585,6 +552,7 @@
     </row>
     <row r="16">
       <c r="B16" s="2"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17">
       <c r="B17" s="2"/>
@@ -594,19 +562,144 @@
     </row>
     <row r="19">
       <c r="B19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="5"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="5"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="5"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="6"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="6"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="6"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="6"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="6"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="6"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="6"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="6"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="5"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="5"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="5"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="5"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="5"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="5"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="5"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="D2"/>
-    <hyperlink r:id="rId2" ref="D3"/>
-    <hyperlink r:id="rId3" ref="D4"/>
-    <hyperlink r:id="rId4" ref="D5"/>
-    <hyperlink r:id="rId5" ref="D6"/>
-    <hyperlink r:id="rId6" ref="D7"/>
-    <hyperlink r:id="rId7" ref="D8"/>
-    <hyperlink r:id="rId8" ref="D9"/>
-    <hyperlink r:id="rId9" ref="D10"/>
+    <hyperlink r:id="rId2" ref="G2"/>
+    <hyperlink r:id="rId3" ref="D3"/>
+    <hyperlink r:id="rId4" ref="D4"/>
+    <hyperlink r:id="rId5" ref="G4"/>
+    <hyperlink r:id="rId6" ref="D5"/>
+    <hyperlink r:id="rId7" ref="D6"/>
+    <hyperlink r:id="rId8" ref="D7"/>
+    <hyperlink r:id="rId9" ref="D8"/>
+    <hyperlink r:id="rId10" ref="D9"/>
+    <hyperlink r:id="rId11" ref="G9"/>
   </hyperlinks>
-  <drawing r:id="rId10"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>